--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>vine</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>serrated</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>palm leaf fan</t>
+          <t>palm-leaf fan</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>emit</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>light fragrance</t>
+          <t>faint fragrance</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pressed together</t>
+          <t>huddled together</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oblong</t>
+          <t>oval</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>strong fragrance</t>
+          <t>rich aroma</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hot summer</t>
+          <t>scorching summer</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>vine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>在看到木瓜樹之前，我以為木瓜也是像西瓜一樣生長在地裏的，或者像黃瓜一樣長在藤蔓上。</t>
+          <t>在我以為木瓜像黃瓜一樣長在藤蔓上。</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>serrated</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉子帶有鋸齒。</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>葉紋清晰可見。</t>
+          <t>葉子上的葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>palm leaf fan</t>
+          <t>palm-leaf fan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>葉子好像一把把大蒲扇。</t>
+          <t>葉子像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>emit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>light fragrance</t>
+          <t>faint fragrance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>木瓜樹的花散發着淡淡的清香。</t>
+          <t>花散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pressed together</t>
+          <t>huddled together</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大大小小的木瓜緊緊地挨在一起。</t>
+          <t>木瓜緊緊地挨在一起。</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>oblong</t>
+          <t>oval</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木瓜是長圓形的，好像一個個欖球。</t>
+          <t>木瓜是長圓形的。</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>木瓜是長圓形的，好像一個個欖球。</t>
+          <t>木瓜好像一個個欖球。</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜。</t>
+          <t>木瓜籽外面有層透明的薄膜。</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜。</t>
+          <t>木瓜籽外面有層透明的薄膜。</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>一粒粒好像烏黑發亮的小眼睛。</t>
+          <t>木瓜籽一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>木瓜有『萬壽果』的稱號。</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>木瓜含豐富維他命C。</t>
+          <t>木瓜含豐富的維他命C。</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
+          <t>木瓜含豐富的胡蘿蔔素。</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
+          <t>木瓜含豐富的蛋白酶。</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>strong fragrance</t>
+          <t>rich aroma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hot summer</t>
+          <t>scorching summer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>也是炎炎夏日中不錯的享受。</t>
+          <t>這也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>也是炎炎夏日中不錯的享受。</t>
+          <t>它是炎炎夏日中的享受。</t>
         </is>
       </c>
     </row>

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated</t>
+          <t>serrated edge</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leaf veins</t>
+          <t>leaf vein</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>huddled together</t>
+          <t>pressed together</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>loving each other</t>
+          <t>loving one another</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>在我以為木瓜像黃瓜一樣長在藤蔓上。</t>
+          <t>在看到木瓜樹之前，我以為木瓜也是像西瓜一樣生長在地裏的，或者像黃瓜一樣長在藤蔓上。</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>木瓜樹的樹幹十分筆直。</t>
+          <t>木瓜樹的樹幹十分筆直，在樹幹的頂部有很多枝葉，下面則沒有葉子。</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated</t>
+          <t>serrated edge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒。</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leaf veins</t>
+          <t>leaf vein</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>葉紋清晰可見。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>葉子上的葉紋清晰可見。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>葉子像一把把大蒲扇。</t>
+          <t>葉子既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>木瓜樹的花散發着淡淡的清香。</t>
+          <t>木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>花散發着淡淡的清香。</t>
+          <t>木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>huddled together</t>
+          <t>pressed together</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>木瓜緊緊地挨在一起。</t>
+          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>loving each other</t>
+          <t>loving one another</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>它們好像相親相愛的兄弟姊妹。</t>
+          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木瓜是長圓形的。</t>
+          <t>木瓜是長圓形的，好像一個個欖球。</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>木瓜好像一個個欖球。</t>
+          <t>木瓜是長圓形的，好像一個個欖球。</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>木瓜籽外面有層透明的薄膜。</t>
+          <t>木瓜籽的外面有層透明的薄膜。</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>木瓜籽外面有層透明的薄膜。</t>
+          <t>木瓜籽的外面有層透明的薄膜。</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>木瓜籽一粒粒好像烏黑發亮的小眼睛。</t>
+          <t>一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>木瓜有『萬壽果』的稱號。</t>
+          <t>木瓜素有『萬壽果』的稱號。</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>木瓜含豐富的維他命C。</t>
+          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>木瓜含豐富的胡蘿蔔素。</t>
+          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>木瓜含豐富的蛋白酶。</t>
+          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>它的果肉非常厚實。</t>
+          <t>它的果肉非常厚實、香氣濃鬱。</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>它的果肉香氣濃鬱。</t>
+          <t>它的果肉非常厚實、香氣濃鬱。</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>這也是炎炎夏日中不錯的享受。</t>
+          <t>加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>它是炎炎夏日中的享受。</t>
+          <t>加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>vines</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated edge</t>
+          <t>serrated edges</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leaf vein</t>
+          <t>leaf veins</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>faint fragrance</t>
+          <t>delicate fragrance</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pressed together</t>
+          <t>nestle together</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>loving one another</t>
+          <t>loving each other</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>oblong shape</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>thin film</t>
+          <t>thin membrane</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rich in</t>
+          <t>rich</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>vines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>木瓜樹的樹幹十分筆直，在樹幹的頂部有很多枝葉，下面則沒有葉子。</t>
+          <t>木瓜樹的樹幹十分筆直。</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated edge</t>
+          <t>serrated edges</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>葉子非常好看，綠綠的，帶有鋸齒。</t>
+          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leaf vein</t>
+          <t>leaf veins</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。</t>
+          <t>木瓜樹的花散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>faint fragrance</t>
+          <t>delicate fragrance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。</t>
+          <t>木瓜樹的花散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pressed together</t>
+          <t>nestle together</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
+          <t>大大小小的木瓜緊緊地挨在一起。</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>loving one another</t>
+          <t>loving each other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
+          <t>大大小小的木瓜好像相親相愛的兄弟姊妹。</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>oval</t>
+          <t>oblong shape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>thin film</t>
+          <t>thin membrane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>一粒粒好像烏黑發亮的小眼睛。</t>
+          <t>一粒粒木瓜籽好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rich in</t>
+          <t>rich</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
+          <t>木瓜含豐富維他命C。</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>它的果肉非常厚實、香氣濃鬱。</t>
+          <t>它的果肉非常厚實。</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
+          <t>加入椰汁做成甜品，是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
+          <t>加入椰汁做成甜品，是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -548,24 +548,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>藤蔓</t>
+          <t>鄉下</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>countryside</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>筆直</t>
+          <t>藤蔓</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>vines</t>
         </is>
       </c>
     </row>
@@ -589,307 +589,211 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>sawtooth edges</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>葉紋</t>
+          <t>清晰可見</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leaf veins</t>
+          <t>clearly visible</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>清晰可見</t>
+          <t>蒲扇</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>clearly visible</t>
+          <t>palm-leaf fan</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>蒲扇</t>
+          <t>撐開</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>palm-leaf fan</t>
+          <t>spread open</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>撐開</t>
+          <t>散發</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>give off</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>散發</t>
+          <t>挨在一起</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>emit</t>
+          <t>press close together</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>清香</t>
+          <t>欖球</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>delicate fragrance</t>
+          <t>rugby ball</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>挨在一起</t>
+          <t>橘黃色</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nestle together</t>
+          <t>orange-yellow</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>相親相愛</t>
+          <t>木瓜籽</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>loving each other</t>
+          <t>papaya seeds</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>長圓形</t>
+          <t>薄膜</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oblong shape</t>
+          <t>thin membrane</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>欖球</t>
+          <t>一粒粒</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rugby ball</t>
+          <t>each one</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>透明</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>transparent</t>
+          <t>has long been known as</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>薄膜</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>thin membrane</t>
+          <t>long-life fruit</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>烏黑發亮</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>shiny black</t>
+          <t>title</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>延年益壽</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>has always been known as</t>
+          <t>prolong life</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>厚實</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>thick and firm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>香氣濃鬱</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>richly fragrant</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>豐富</t>
+          <t>炎炎夏日</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rich</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>胡蘿蔔素</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>carotene</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>蛋白酶</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>protease</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>據說</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>it is said</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>延年益壽</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>prolong life</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>厚實</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>thick and firm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>香氣濃鬱</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rich aroma</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>炎炎夏日</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>scorching summer</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>享受</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>enjoyment</t>
+          <t>scorching summer days</t>
         </is>
       </c>
     </row>
@@ -904,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -952,44 +856,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>藤蔓</t>
+          <t>鄉下</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>countryside</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>téng wàn</t>
+          <t>xiāng xià</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>在看到木瓜樹之前，我以為木瓜也是像西瓜一樣生長在地裏的，或者像黃瓜一樣長在藤蔓上。</t>
+          <t>三上 ： 木瓜樹（第三十八頁）
+在鄉下的表叔家，我第一次見到木瓜樹。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>筆直</t>
+          <t>藤蔓</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>straight</t>
+          <t>vines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bǐ zhí</t>
+          <t>téng wàn</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>木瓜樹的樹幹十分筆直。</t>
+          <t>或者像黃瓜一樣長在藤蔓上。</t>
         </is>
       </c>
     </row>
@@ -1023,7 +928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>sawtooth edges</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1033,557 +938,381 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>葉紋</t>
+          <t>清晰可見</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leaf veins</t>
+          <t>clearly visible</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yè wén</t>
+          <t>qīng xī kě jiàn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
+          <t>葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>清晰可見</t>
+          <t>蒲扇</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>clearly visible</t>
+          <t>palm-leaf fan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>qīng xī kě jiàn</t>
+          <t>pú shàn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>葉子帶有鋸齒，葉紋清晰可見。</t>
+          <t>既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>蒲扇</t>
+          <t>撐開</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>palm-leaf fan</t>
+          <t>spread open</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pú shàn</t>
+          <t>chēng kāi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>葉子既像巨大的手掌，又好像一把把大蒲扇。</t>
+          <t>遠遠看去好像一把撐開的大傘。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>撐開</t>
+          <t>散發</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>give off</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chēng kāi</t>
+          <t>sàn fā</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>遠遠看去好像一把撐開的大傘。</t>
+          <t>木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>散發</t>
+          <t>挨在一起</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emit</t>
+          <t>press close together</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sàn fā</t>
+          <t>āi zài yì qǐ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>木瓜樹的花散發着淡淡的清香。</t>
+          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>清香</t>
+          <t>欖球</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>delicate fragrance</t>
+          <t>rugby ball</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>qīng xiāng</t>
+          <t>lǎn qiú</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>木瓜樹的花散發着淡淡的清香。</t>
+          <t>木瓜是長圓形的，好像一個個欖球。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>挨在一起</t>
+          <t>橘黃色</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nestle together</t>
+          <t>orange-yellow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>āi zài yì qǐ</t>
+          <t>jú huáng sè</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大大小小的木瓜緊緊地挨在一起。</t>
+          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>相親相愛</t>
+          <t>木瓜籽</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>loving each other</t>
+          <t>papaya seeds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xiāng qīn xiāng ài</t>
+          <t>mù guā zǐ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>大大小小的木瓜好像相親相愛的兄弟姊妹。</t>
+          <t>木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>長圓形</t>
+          <t>薄膜</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>oblong shape</t>
+          <t>thin membrane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>zhǎng yuán xíng</t>
+          <t>báo mó</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木瓜是長圓形的，好像一個個欖球。</t>
+          <t>木瓜籽的外面有層透明的薄膜。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>欖球</t>
+          <t>一粒粒</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rugby ball</t>
+          <t>each one</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lǎn qiú</t>
+          <t>yī lì lì</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>木瓜是長圓形的，好像一個個欖球。</t>
+          <t>一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>透明</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>transparent</t>
+          <t>has long been known as</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tòu míng</t>
+          <t>sù yǒu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜。</t>
+          <t>木瓜素有『萬壽果』的稱號。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>薄膜</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>thin membrane</t>
+          <t>long-life fruit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>báo mó</t>
+          <t>wàn shòu guǒ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜。</t>
+          <t>木瓜素有『萬壽果』的稱號。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>烏黑發亮</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>shiny black</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wū hēi fā liàng</t>
+          <t>chēng hào</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>一粒粒木瓜籽好像烏黑發亮的小眼睛。</t>
+          <t>木瓜素有『萬壽果』的稱號。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>延年益壽</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>has always been known as</t>
+          <t>prolong life</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sù yǒu</t>
+          <t>yán nián yì shòu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>厚實</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>thick and firm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wàn shòu guǒ</t>
+          <t>hòu shí</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>它的果肉非常厚實、香氣濃鬱。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>香氣濃鬱</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>richly fragrant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chēng hào</t>
+          <t>xiāng qì nóng yù</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>它的果肉非常厚實、香氣濃鬱。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>豐富</t>
+          <t>炎炎夏日</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rich</t>
+          <t>scorching summer days</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fēng fù</t>
+          <t>yán yán xià rì</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>木瓜含豐富維他命C。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>胡蘿蔔素</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>carotene</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>hú luó bó sù</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>蛋白酶</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>protease</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>dàn bái méi</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>木瓜含豐富維他命C、胡蘿蔔素以及蛋白酶。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>據說</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>it is said</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>jù shuō</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>據說多喫可以延年益壽。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>延年益壽</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prolong life</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>yán nián yì shòu</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>據說多喫可以延年益壽。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>厚實</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>thick and firm</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>hòu shí</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>它的果肉非常厚實。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>香氣濃鬱</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>rich aroma</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>xiāng qì nóng yù</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>它的果肉非常厚實、香氣濃鬱。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>炎炎夏日</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>scorching summer</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>yán yán xià rì</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>加入椰汁做成甜品，是炎炎夏日中不錯的享受。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>享受</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>enjoyment</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>xiǎng shòu</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>加入椰汁做成甜品，是炎炎夏日中不錯的享受。</t>
+          <t>也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sawtooth edges</t>
+          <t>serrated edges</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>opened</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>emits</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>press close together</t>
+          <t>nestle together</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rugby ball</t>
+          <t>rugby balls</t>
         </is>
       </c>
     </row>
@@ -704,48 +704,48 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>一粒粒</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>each one</t>
+          <t>has long been known as</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>has long been known as</t>
+          <t>longevity fruit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>long-life fruit</t>
+          <t>title</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>甜品</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>dessert</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>richly fragrant</t>
+          <t>rich aroma</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>或者像黃瓜一樣長在藤蔓上。</t>
+          <t>在看到木瓜樹之前，我以為木瓜也是像西瓜一樣生長在地裏的，或者像黃瓜一樣長在藤蔓上。</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>它的葉柄非常長，中間是空的。</t>
+          <t>木瓜樹的樹幹十分筆直，在樹幹的頂部有很多枝葉，下面則沒有葉子，它的葉柄非常長，中間是空的。</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sawtooth edges</t>
+          <t>serrated edges</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>葉子非常好看，綠綠的，帶有鋸齒。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>既像巨大的手掌，又好像一把把大蒲扇。</t>
+          <t>葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>opened</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>遠遠看去好像一把撐開的大傘。</t>
+          <t>因為它的葉子、果實都是長在樹頂，所以遠遠看去好像一把撐開的大傘。</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>emits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>press close together</t>
+          <t>nestle together</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹。</t>
+          <t>到了夏天，木瓜樹上結滿了果實，大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹，看上去十分熱鬧。</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rugby ball</t>
+          <t>rugby balls</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽。</t>
+          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽，木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
+          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽，木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
@@ -1136,95 +1136,95 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>木瓜籽的外面有層透明的薄膜。</t>
+          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽，木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>一粒粒</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>each one</t>
+          <t>has long been known as</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yī lì lì</t>
+          <t>sù yǒu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>一粒粒好像烏黑發亮的小眼睛。</t>
+          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>has long been known as</t>
+          <t>longevity fruit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sù yǒu</t>
+          <t>wàn shòu guǒ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>long-life fruit</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wàn shòu guǒ</t>
+          <t>chēng hào</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>甜品</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>chēng hào</t>
+          <t>tián pǐn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號。</t>
+          <t>它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>據說多喫可以延年益壽。</t>
+          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>它的果肉非常厚實、香氣濃鬱。</t>
+          <t>它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>richly fragrant</t>
+          <t>rich aroma</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>它的果肉非常厚實、香氣濃鬱。</t>
+          <t>它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>也是炎炎夏日中不錯的享受。</t>
+          <t>它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
     </row>

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>vine</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>serrated edge</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opened</t>
+          <t>spread open</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emits</t>
+          <t>give off</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rugby balls</t>
+          <t>rugby ball</t>
         </is>
       </c>
     </row>
@@ -704,48 +704,48 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>一粒粒</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>has long been known as</t>
+          <t>each one</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>have long been known as</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>longevity fruit</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>甜品</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>title</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>scorching summer days</t>
+          <t>scorching summer</t>
         </is>
       </c>
     </row>
@@ -871,8 +871,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>三上 ： 木瓜樹（第三十八頁）
-在鄉下的表叔家，我第一次見到木瓜樹。</t>
+          <t>在鄉下的表叔家，我第一次見到木瓜樹。</t>
         </is>
       </c>
     </row>
@@ -884,7 +883,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vines</t>
+          <t>vine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -928,7 +927,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated edges</t>
+          <t>serrated edge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -994,7 +993,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>opened</t>
+          <t>spread open</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1016,7 +1015,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emits</t>
+          <t>give off</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1060,7 +1059,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rugby balls</t>
+          <t>rugby ball</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1143,39 +1142,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>素有</t>
+          <t>一粒粒</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>has long been known as</t>
+          <t>each one</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sù yǒu</t>
+          <t>yī lì lì</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
+          <t>切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽，木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>萬壽果</t>
+          <t>素有</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>have long been known as</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wàn shòu guǒ</t>
+          <t>sù yǒu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1187,17 +1186,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>稱號</t>
+          <t>萬壽果</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>longevity fruit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>chēng hào</t>
+          <t>wàn shòu guǒ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1209,22 +1208,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>甜品</t>
+          <t>稱號</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>tián pǐn</t>
+          <t>chēng hào</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
+          <t>木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1301,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>scorching summer days</t>
+          <t>scorching summer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>vines</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>serrated edge</t>
+          <t>serrated edges</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>opened up</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>gives off</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nestle together</t>
+          <t>nestled together</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>each one</t>
+          <t>each seed</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>have long been known as</t>
+          <t>has long been known as</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>fruit of longevity</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>thick and firm</t>
+          <t>thick and tender</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>scorching summer</t>
+          <t>hot summer days</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,8 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>在鄉下的表叔家，我第一次見到木瓜樹。</t>
+          <t>三上 ： 木瓜樹（第三十八頁）
+在鄉下的表叔家，我第一次見到木瓜樹。</t>
         </is>
       </c>
     </row>
@@ -883,7 +884,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>vine</t>
+          <t>vines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -927,7 +928,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>serrated edge</t>
+          <t>serrated edges</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>spread open</t>
+          <t>opened up</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1015,7 +1016,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>give off</t>
+          <t>gives off</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1037,7 +1038,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nestle together</t>
+          <t>nestled together</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1147,7 +1148,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>each one</t>
+          <t>each seed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1169,7 +1170,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>have long been known as</t>
+          <t>has long been known as</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1191,7 +1192,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>longevity fruit</t>
+          <t>fruit of longevity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1257,7 +1258,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>thick and firm</t>
+          <t>thick and tender</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>scorching summer</t>
+          <t>hot summer days</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">

--- a/content-pipeline/inputs/book04/b04_ch14_final.xlsx
+++ b/content-pipeline/inputs/book04/b04_ch14_final.xlsx
@@ -543,7 +543,7 @@
 在鄉下的表叔家，我第一次見到木瓜樹。
 在看到木瓜樹之前，我以為木瓜也是像西瓜一樣生長在地裏的，或者像黃瓜一樣長在藤蔓上。原來，它們是長在一棵高高的小樹上。木瓜樹的樹幹十分筆直，在樹幹的頂部有很多枝葉，下面則沒有葉子，它的葉柄非常長，中間是空的。葉子非常好看，綠綠的，帶有鋸齒，葉紋清晰可見，既像巨大的手掌，又好像一把把大蒲扇。因為它的葉子、果實都是長在樹頂，所以遠遠看去好像一把撐開的大傘。
 木瓜樹的花是淡黃色的，小小的，散發着淡淡的清香。到了夏天，木瓜樹上結滿了果實，大大小小的木瓜緊緊地挨在一起，好像相親相愛的兄弟姊妹，看上去十分熱鬧。木瓜是長圓形的，好像一個個欖球。它們成熟以前是綠色的，慢慢的就變成黃色。切開來，會發現裏面有橘黃色的果肉和很多黑色的小籽，木瓜籽的外面有層透明的薄膜，一粒粒好像烏黑發亮的小眼睛。
-木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多喫可以延年益壽。它的果肉非常厚實、香氣濃鬱，喫一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
+木瓜素有『萬壽果』的稱號，含豐富維他命C、胡蘿蔔素以及蛋白酶，據說多吃可以延年益壽。它的果肉非常厚實、香氣濃郁，吃一口軟軟的，如果加入椰汁做成甜品食用，也是炎炎夏日中不錯的享受。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>香氣濃鬱</t>
+          <t>香氣濃郁</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
